--- a/Spec documents/OPEN Pillar.xlsx
+++ b/Spec documents/OPEN Pillar.xlsx
@@ -2,32 +2,58 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TrueScan-FoodScanner\TruScore logic\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leigh\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B52F87F-EDFD-448A-B297-AB4BF3FFD08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B61AEF8-B81E-487B-88C2-805AFC6DF289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33735" yWindow="750" windowWidth="23055" windowHeight="14730" xr2:uid="{BB904EBE-EC27-4577-B392-A9CA08F804A9}"/>
+    <workbookView xWindow="29745" yWindow="690" windowWidth="25065" windowHeight="14730" xr2:uid="{8B856D29-CDA2-9345-9E9F-B4C972BD0AB2}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Open_Scoring_Specification_v14" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <definedNames>
+    <definedName name="Open_Pillar_Specification_v13" localSheetId="0">Open_Scoring_Specification_v14!$A$1:$I$20</definedName>
+  </definedNames>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
+  <connection id="1" xr16:uid="{31407F1B-58B7-1848-9EFC-57D683D0FB7C}" name="Open_Pillar_Specification_v13" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr codePage="65001" sourceFile="/Users/matthewgold/Desktop/TruScan/Software Development/Open_Pillar_Specification_v13.rtf" tab="0" qualifier="none" delimiter="|">
+      <textFields>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+</connections>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="63">
-  <si>
-    <t xml:space="preserve">Pillar (25 pts) </t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
+  <si>
+    <t xml:space="preserve"> Pillar (25 pts) </t>
   </si>
   <si>
     <t xml:space="preserve"> Data Element </t>
@@ -60,34 +86,295 @@
     <t xml:space="preserve"> Base Score </t>
   </si>
   <si>
-    <t xml:space="preserve"> Slightly positive neutral; assumes transparent till hidden </t>
+    <t>Internal logic baseline applied before evidence-based adjustments</t>
   </si>
   <si>
     <t xml:space="preserve"> Internal Logic (No external source) </t>
   </si>
   <si>
-    <t xml:space="preserve"> Scaled OECD G20 avg ~60/100 (2025 supply chains); optimistic fair to indies </t>
+    <t>Baseline transparency score before disclosure adjustments</t>
   </si>
   <si>
     <t xml:space="preserve"> N/A </t>
   </si>
   <si>
-    <t xml:space="preserve"> 15 (uniform) </t>
+    <t xml:space="preserve"> 15 (Base Score uniform across all pillars) </t>
+  </si>
+  <si>
+    <t>A baseline is not a positive transparency endorsement; it is a neutral starting position used for consistency across pillars.</t>
   </si>
   <si>
     <t xml:space="preserve"> 1. Always starting point; adjustments added/subtracted. </t>
   </si>
   <si>
+    <t xml:space="preserve"> Ingredients Disclosure </t>
+  </si>
+  <si>
+    <t>Approved label standards and OFF ingredients text / ingredient presence fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FDA (US labeling), Health Canada, FSANZ (AU/NZ), UK FSA/EFSA, MHLW (Japan), CFS (HK), SFA (SG) &gt; Country/Global OFF </t>
+  </si>
+  <si>
+    <t>This measures the presence and clarity of core ingredient disclosure, not the health quality of the ingredients themselves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ingredients_text (present) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Present=+2, none=-3 </t>
+  </si>
+  <si>
+    <t>Rewards products that make core ingredient information available</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. Country OFF &gt; 2. Global OFF &gt; 3. Local govt regs (e.g., MHLW Japan) &gt; 4. User subs if gaps; binary present/none. </t>
+  </si>
+  <si>
     <t xml:space="preserve"> Hidden Terms </t>
   </si>
   <si>
-    <t xml:space="preserve"> No hidden terms like parfum/aroma </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 50% disgust on parfum (X sentiment) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ingredients_text (match count for parfum/aroma/flavor/natural flavor/natural flavour/proprietary blend/secret formula/artificial flavor/essence/spice/extract/additive e.g. E621) </t>
+    <t xml:space="preserve"> FDA (US), Health Canada, FSANZ (AU/NZ), UK FSA/EFSA, MHLW (Japan), CFS (HK irritants), SFA (SG) &gt; Country/Global OFF </t>
+  </si>
+  <si>
+    <t>Penalises harder-to-interpret or vague ingredient disclosure and rewards clearer disclosure where supported by the ingredient list</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ingredients_text (present) 
+  match_rules:
+    case_insensitive: true
+    unicode_normalize: true
+    whole_word_or_exact_phrase_only: true
+    no_substring_matching: true
+  exact_phrases:
+    generic_flavour_terms:
+      - flavour
+      - flavor
+      - flavours
+      - flavors
+      - flavouring
+      - flavoring
+      - flavourings
+      - flavorings
+      - natural flavour
+      - natural flavor
+      - natural flavours
+      - natural flavors
+      - natural flavouring
+      - natural flavoring
+      - natural flavourings
+      - natural flavorings
+      - artificial flavour
+      - artificial flavor
+      - artificial flavours
+      - artificial flavors
+      - artificial flavouring
+      - artificial flavoring
+      - artificial flavourings
+      - artificial flavorings
+      - natural and artificial flavour
+      - natural and artificial flavor
+      - natural &amp; artificial flavour
+      - natural &amp; artificial flavor
+      - natural and artificial flavours
+      - natural and artificial flavors
+      - natural &amp; artificial flavours
+      - natural &amp; artificial flavors
+      - smoke flavour
+      - smoke flavor
+      - smoke flavours
+      - smoke flavors
+      - smoke flavouring
+      - smoke flavoring
+      - flavouring substance
+      - flavoring substance
+      - flavouring substances
+      - flavoring substances
+      - flavouring preparation
+      - flavoring preparation
+      - flavouring preparations
+      - flavoring preparations
+      - thermal process flavouring
+      - thermal process flavoring
+      - thermal process flavourings
+      - thermal process flavorings
+      - nature-identical flavour
+      - nature-identical flavor
+      - nature-identical flavours
+      - nature-identical flavors
+      - nature-identical flavouring
+      - nature-identical flavoring
+      - nature identical flavour
+      - nature identical flavor
+      - nature identical flavours
+      - nature identical flavors
+      - nature identical flavouring
+      - nature identical flavoring
+      - permitted flavouring
+      - permitted flavoring
+      - permitted flavourings
+      - permitted flavorings
+      - permitted flavouring substance
+      - permitted flavoring substance
+      - permitted flavouring substances
+      - permitted flavoring substances
+      - aroma
+      - aromas
+      - natural aroma
+      - natural aromas
+      - artificial aroma
+      - artificial aromas
+    generic_spice_herb_seasoning_terms:
+      - spice
+      - spices
+      - mixed spice
+      - mixed spices
+      - spice blend
+      - spice blends
+      - spice extractive
+      - spice extractives
+      - seasoning
+      - seasonings
+      - seasoning blend
+      - seasoning blends
+      - herb
+      - herbs
+      - mixed herb
+      - mixed herbs
+      - herb blend
+      - herb blends
+    generic_extract_terms_generic_only:
+      - extract
+      - extracts
+      - extractive
+      - extractives
+      - essence
+      - essences
+      - oleoresin
+      - oleoresins
+      - distillate
+      - distillates
+      - essential oil
+      - essential oils
+      - botanical extract
+      - botanical extracts
+      - plant extract
+      - plant extracts
+      - fruit extract
+      - fruit extracts
+      - vegetable extract
+      - vegetable extracts
+      - infusion
+      - infusions
+    additive_class_terms_standalone_or_code_only:
+      - additive
+      - additives
+      - food additive
+      - food additives
+      - acid
+      - acids
+      - food acid
+      - food acids
+      - acidity regulator
+      - acidity regulators
+      - anti-caking agent
+      - anti-caking agents
+      - anticaking agent
+      - anticaking agents
+      - antioxidant
+      - antioxidants
+      - bulking agent
+      - bulking agents
+      - colour
+      - colours
+      - color
+      - colors
+      - colouring
+      - colourings
+      - coloring
+      - colorings
+      - emulsifier
+      - emulsifiers
+      - enzyme
+      - enzymes
+      - firming agent
+      - firming agents
+      - flavour enhancer
+      - flavour enhancers
+      - flavor enhancer
+      - flavor enhancers
+      - flour treatment agent
+      - flour treatment agents
+      - foaming agent
+      - foaming agents
+      - gelling agent
+      - gelling agents
+      - glazing agent
+      - glazing agents
+      - humectant
+      - humectants
+      - mineral salt
+      - mineral salts
+      - preservative
+      - preservatives
+      - propellant
+      - propellants
+      - raising agent
+      - raising agents
+      - sequestrant
+      - sequestrants
+      - stabiliser
+      - stabilisers
+      - stabilizer
+      - stabilizers
+      - sweetener
+      - sweeteners
+      - thickener
+      - thickeners
+  regex_patterns:
+    additive_code_only:
+      - "\\bE\\s?\\d{3,4}[a-z]?\\b"
+      - "\\bINS\\s?\\d{3,4}[a-z]?\\b"</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1=-4, 2=-8, &gt;=3=-11; if NOVA&gt;=3; zero hidden &amp; NOVA1-2 = +4; zero hidden &amp; NOVA 3-4 = +2 </t>
+  </si>
+  <si>
+    <t>Keep the hidden-terms list version-controlled and narrowly defined. The guardrails matter more than the list itself:
+extract, essence, oleoresin, distillate, essential oil, infusion should only count when they are generic. Count extract; do not count vanilla extract.
+Additive class names should only count when they are standalone or followed only by a code. Count emulsifier (471) and E621; do not count emulsifier (soy lecithin) or monosodium glutamate.
+Use whole-word matching only. Count spice; do not hit allspice.
+Count per ingredient token, not per repeated substring inside one token.
+Examples:
+Count: flavour, natural flavouring, spices, seasoning, spice extractives, emulsifier (471), E621, INS 621
+Do not count: vanilla extract, lemon essence, paprika extract, caramel colour, monosodium glutamate, preservative (potassium sorbate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. Country OFF &gt; 2. Global OFF &gt; 3. Local govt (e.g., SFA SG); deduct if match; conditional NOVA tie; reward if zero hidden. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nutritional Information </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Full nutritional information disclosed with benchmarking (e.g. per serve, per 45g per 100g) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FDA (US nutrition labels), Health Canada, FSANZ (AU/NZ), UK FSA/EFSA, MHLW (Japan), CFS (HK), SFA (SG) &gt; Country/Global OFF </t>
+  </si>
+  <si>
+    <t>Rewards products that disclose usable nutritional information</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> nutrients (complete array with _100g keys and serving_size) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Complete (e.g.  per 100g/serve benchmarks)=+3, partial=+1, none=-3 </t>
+  </si>
+  <si>
+    <t>This measures the availability of nutrition information, not whether the nutrition outcome is good or bad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. Country OFF &gt; 2. Global OFF; bonus if nutrients complete with _100g/serve; partial if only totals. </t>
   </si>
   <si>
     <t xml:space="preserve"> Origins </t>
@@ -96,172 +383,97 @@
     <t xml:space="preserve"> Full origins disclosed; supply chain transparency </t>
   </si>
   <si>
+    <t xml:space="preserve"> FDA (US), Health Canada, FSANZ (AU/NZ origins), UK FSA/EFSA, MHLW (Japan), CFS (HK), SFA (SG) &gt; Country/Global OFF </t>
+  </si>
+  <si>
     <t xml:space="preserve"> 30% origins distrust (geopolitics X concern 2025) </t>
   </si>
   <si>
     <t xml:space="preserve"> origins_tags (present and complete) </t>
   </si>
   <si>
-    <t xml:space="preserve"> Brand Ownership </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Full brand/parent disclosed; no opacity </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> brands_tags (parent map present) </t>
+    <t xml:space="preserve"> No origin=-4, complete=+4 bonus </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Studies defend; heavy geo for supply chain shocks; GS1 API post-MVP (costs &gt;$5k, post-2027 enhancement for AI-422 origin/AI-423 processing deduct -4 missing). Softer bonus/deduct to balance per beta. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. Country OFF &gt; 2. Global OFF &gt; 3. Local govt tags (e.g., FSANZ AU); deduct if missing, bonus if complete; GS1 post-MVP. </t>
   </si>
   <si>
     <t xml:space="preserve"> Overall Pillar Cap </t>
   </si>
   <si>
-    <t xml:space="preserve"> Allows wake-up viral on low scores for bad deducts </t>
+    <t>Minimum score returned after all adjust,ents from base score.</t>
   </si>
   <si>
     <t xml:space="preserve"> Min 0 (floor after all adjustments) </t>
   </si>
   <si>
+    <t>The cap/floor controls output range only and does not imply that all relevant transparency issues are fully captured.</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 1. Applied after all adjustments; overrides if &lt;0. </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Ingredients Disclosure </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Full list disclosed digitally; no placeholders </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FDA (US labeling), Health Canada, FSANZ (AU/NZ), UK FSA/EFSA, MHLW (Japan), CFS (HK), SFA (SG) &gt; Country/Global OFF </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 70% consumers value lists (trust killer X 2025) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ingredients_text (present) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1. Country OFF &gt; 2. Global OFF &gt; 3. Local govt regs (e.g., MHLW Japan) &gt; 4. User subs if gaps; binary present/none. </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FDA (US), Health Canada, FSANZ (AU/NZ), UK FSA/EFSA, MHLW (Japan), CFS (HK irritants), SFA (SG) &gt; Country/Global OFF </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1. Country OFF &gt; 2. Global OFF &gt; 3. Local govt (e.g., SFA SG); deduct if match; conditional NOVA tie; reward if zero hidden. </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FDA (US), Health Canada, FSANZ (AU/NZ origins), UK FSA/EFSA, MHLW (Japan), CFS (HK), SFA (SG) &gt; Country/Global OFF </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1. Country OFF &gt; 2. Global OFF &gt; 3. Local govt tags (e.g., FSANZ AU); deduct if missing, bonus if complete; GS1 post-MVP. </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Country/Global OFF </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1. Country OFF &gt; 2. Global OFF; deduct if hidden parent; GS1 post-MVP for ownership. </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Uniform 15 consistency; OECD defends without negativity; fair to indies avoids X backlash on bias. Ditched geo-weight for MVP'97embed mandates in elements. </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Present=+2, none=-3 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Modest deduct for no digital record (defensible if not public); accounts for possible packaging list not digitized. Adjusted to -3 for fairness on sparse DB entries. </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1=-4, 2=-8, &gt;=3=-11; if NOVA&gt;=3; zero hidden &amp; NOVA1-2 = +4; zero hidden &amp; NOVA3-4 = +2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Studies/X defend count; geo local tags heavy. Comprehensive hidden catalog conceals nasties'97focus opacity proxy. Mandate embed: +4/+2 rewards for zero hidden tied to NOVA. Softer deducts for balance per beta insights. </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Nutritional Information </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Full nutritional information disclosed with benchmarks </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FDA (US nutrition labels), Health Canada, FSANZ (AU/NZ), UK FSA/EFSA, MHLW (Japan), CFS (HK), SFA (SG) &gt; Country/Global OFF </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 55% distrust hidden nutrients/sugar (obesity concerns X 2025) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> nutrients (complete array with _100g keys and serving_size) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Complete (per 100g/serve benchmarks)=+3, partial=+1, none=-3 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Rewards transparent benchmarks per WHO/EFSA studies; virality on sugar hides without overkill. Ties to G20 mandates (e.g., EU per-100g). </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1. Country OFF &gt; 2. Global OFF; bonus if nutrients complete with _100g/serve; partial if only totals. </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> No origin=-4, complete=+4 bonus </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Studies defend; heavy geo for supply chain shocks; GS1 API post-MVP (costs &gt;$5k, post-2027 enhancement for AI-422 origin/AI-423 processing deduct -4 missing). Softer bonus/deduct to balance per beta. </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 70% hate indie illusions (10 corps control 33k products'97X sentiment 2025) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Hidden/opaque parent=-3 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sentiment defends; virality on "Owned By Nestle Alert" shares. Mandate embed here'97no base complexity. Softer deduct for fairness. </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Caps final Open score at min 0; zero "opacity alert" callout on hidden crap'97viral rage without overkill. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <sz val="10"/>
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -270,23 +482,23 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -305,6 +517,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="Open_Pillar_Specification_v13" connectionId="1" xr16:uid="{0D217A95-2799-E343-A8AB-4052E0CB6EC1}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -316,39 +532,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -400,7 +616,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -511,13 +727,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -526,6 +735,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -590,269 +806,257 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C149CC-AACB-4AE3-BE1E-B17C8CB58521}">
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46D1E38F-6BD0-364D-B370-E8E7551601D3}">
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.85546875" customWidth="1"/>
-    <col min="3" max="3" width="24.85546875" customWidth="1"/>
-    <col min="4" max="4" width="27.140625" customWidth="1"/>
-    <col min="5" max="5" width="29" customWidth="1"/>
-    <col min="6" max="6" width="28.85546875" customWidth="1"/>
-    <col min="7" max="7" width="26.42578125" customWidth="1"/>
-    <col min="8" max="8" width="31.85546875" customWidth="1"/>
-    <col min="9" max="9" width="28" customWidth="1"/>
-    <col min="10" max="10" width="27.85546875" customWidth="1"/>
-    <col min="11" max="11" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="58.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="45" style="2" customWidth="1"/>
+    <col min="6" max="6" width="54.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="52.875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="54.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="44.625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="5" t="s">
+    <row r="1" spans="1:9" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="D10" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="E10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="F10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="G10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="H10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="I10" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="122.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="4" t="s">
+    <row r="11" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="F11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="G11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="H11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="6"/>
+      <c r="B12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="408" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6"/>
+      <c r="B13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
+      <c r="B15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>16</v>
+      <c r="F15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="142.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="2" t="s">
+    <row r="16" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="C16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H16" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="I16" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="4"/>
-      <c r="D7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="C8" s="4"/>
-      <c r="D8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="C2:C8"/>
+  <mergeCells count="1">
+    <mergeCell ref="A11:A16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
